--- a/artfynd/A 58155-2025 artfynd.xlsx
+++ b/artfynd/A 58155-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125539239</v>
+        <v>125539229</v>
       </c>
       <c r="B2" t="n">
-        <v>92526</v>
+        <v>91859</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>112</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>599889</v>
+        <v>600039</v>
       </c>
       <c r="R2" t="n">
-        <v>7054625</v>
+        <v>7054564</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126125250</v>
+        <v>125539230</v>
       </c>
       <c r="B3" t="n">
-        <v>78980</v>
+        <v>92208</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,34 +783,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Lövsjöbäcken, Ång</t>
+          <t>Bysjön-Lövsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>600123</v>
+        <v>600030</v>
       </c>
       <c r="R3" t="n">
-        <v>7054194</v>
+        <v>7054566</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -837,12 +837,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-05-29</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-05-29</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126125243</v>
+        <v>125539225</v>
       </c>
       <c r="B4" t="n">
-        <v>91245</v>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,14 +900,14 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Lövsjöbäcken, Ång</t>
+          <t>Bysjön-Lövsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>600068</v>
+        <v>600039</v>
       </c>
       <c r="R4" t="n">
-        <v>7054218</v>
+        <v>7054564</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -934,12 +934,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-05-29</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-05-29</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126125248</v>
+        <v>126125243</v>
       </c>
       <c r="B5" t="n">
-        <v>56840</v>
+        <v>91909</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,42 +977,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102612</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Lövsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>600244</v>
+        <v>600068</v>
       </c>
       <c r="R5" t="n">
-        <v>7054641</v>
+        <v>7054218</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1068,6 +1060,917 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>126125237</v>
+      </c>
+      <c r="B6" t="n">
+        <v>83173</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Lövsjöbäcken, Ång</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>600038</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7054626</v>
+      </c>
+      <c r="S6" t="n">
+        <v>15</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>125539239</v>
+      </c>
+      <c r="B7" t="n">
+        <v>93197</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Bysjön-Lövsjöbäcken, Ång</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>599889</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7054625</v>
+      </c>
+      <c r="S7" t="n">
+        <v>15</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-05-29</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-05-29</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>126125250</v>
+      </c>
+      <c r="B8" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Lövsjöbäcken, Ång</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>600123</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7054194</v>
+      </c>
+      <c r="S8" t="n">
+        <v>15</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>126125245</v>
+      </c>
+      <c r="B9" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Lövsjöbäcken, Ång</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>600027</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7054254</v>
+      </c>
+      <c r="S9" t="n">
+        <v>15</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>126125247</v>
+      </c>
+      <c r="B10" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Lövsjöbäcken, Ång</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>600058</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7054262</v>
+      </c>
+      <c r="S10" t="n">
+        <v>15</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>125498899</v>
+      </c>
+      <c r="B11" t="n">
+        <v>80460</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6461</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Norrlandslav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Nephroma arcticum</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Lövsjöbäcken, Ång</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>600181</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7054404</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-05-29</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>10:48</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-05-29</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>10:48</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>126125244</v>
+      </c>
+      <c r="B12" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Lövsjöbäcken, Ång</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>600060</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7054259</v>
+      </c>
+      <c r="S12" t="n">
+        <v>15</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Äldre ringhack, gran</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>126125248</v>
+      </c>
+      <c r="B13" t="n">
+        <v>57132</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Lövsjöbäcken, Ång</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>600244</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7054641</v>
+      </c>
+      <c r="S13" t="n">
+        <v>15</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>125502458</v>
+      </c>
+      <c r="B14" t="n">
+        <v>58439</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>103018</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Svartvit flugsnappare</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Ficedula hypoleuca</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Pallas, 1764)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Lövsjöbäcken, Lövsjöbäcken, Ång</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>600004</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7054538</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-05-29</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>12:22</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-05-29</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>12:22</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 58155-2025 artfynd.xlsx
+++ b/artfynd/A 58155-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AZ14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125539229</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125539230</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125539225</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126125243</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126125237</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125539239</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126125250</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126125245</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1545,6 +1590,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126125247</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1652,6 +1702,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125498899</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1759,6 +1814,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126125244</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1864,6 +1924,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126125248</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1971,8 +2036,28 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125502458</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>